--- a/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_Raw.xlsx
+++ b/CPRD Raw Analysis/Results/SecondaryCareAnalysis/OP/Table1_OP_Raw.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,7 +384,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>115256 (68.64%)</t>
+          <t>115256 (67.67%)</t>
         </is>
       </c>
     </row>
@@ -401,7 +401,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>49309 (29.37%)</t>
+          <t>49309 (28.95%)</t>
         </is>
       </c>
     </row>
@@ -413,12 +413,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Attended subsequent tele consultation</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1900 (1.13%)</t>
+          <t>2415 (1.42%)</t>
         </is>
       </c>
     </row>
@@ -430,12 +430,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Attended first tele consultation</t>
+          <t>Attended subsequent tele consultation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>838 (0.5%)</t>
+          <t>1900 (1.12%)</t>
         </is>
       </c>
     </row>
@@ -447,63 +447,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Attended but first/subsequent/tele unknown</t>
+          <t>Attended first tele consultation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>603 (0.36%)</t>
+          <t>838 (0.49%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Attended or Did Not Attend</t>
+          <t>Attendance Type</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Seen – attended on time or, if late, before the relevant care professional was ready to see the patient</t>
+          <t>Attended but first/subsequent/tele unknown</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>167906 (100%)</t>
+          <t>603 (0.35%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>First Attendance</t>
+          <t>Attended or Did Not Attend</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Follow-up attendance face to face</t>
+          <t>Seen – attended on time or, if late, before the relevant care professional was ready to see the patient</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>115256 (68.64%)</t>
+          <t>167906 (98.58%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>First Attendance</t>
+          <t>Attended or Did Not Attend</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First attendance face to face</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>49309 (29.37%)</t>
+          <t>2415 (1.42%)</t>
         </is>
       </c>
     </row>
@@ -515,12 +515,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Follow-up telephone or telemedicine consultation</t>
+          <t>Follow-up attendance face to face</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1900 (1.13%)</t>
+          <t>115256 (67.67%)</t>
         </is>
       </c>
     </row>
@@ -532,12 +532,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>First telephone or telemedicine consultation</t>
+          <t>First attendance face to face</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>838 (0.5%)</t>
+          <t>49309 (28.95%)</t>
         </is>
       </c>
     </row>
@@ -549,114 +549,114 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Not known (from 2008/09)</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>603 (0.36%)</t>
+          <t>2415 (1.42%)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Main Diagnosis</t>
+          <t>First Attendance</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R69X-Unknown and unspecified causes of morbidity</t>
+          <t>Follow-up telephone or telemedicine consultation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>164190 (97.79%)</t>
+          <t>1900 (1.12%)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Main Diagnosis</t>
+          <t>First Attendance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other Main Diagnosis</t>
+          <t>First telephone or telemedicine consultation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3716 (1.62%)</t>
+          <t>838 (0.49%)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>First Attendance</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Other Main Procedure</t>
+          <t>Not known (from 2008/09)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16671 (32.33%)</t>
+          <t>603 (0.35%)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Diagnosis</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>X997-NA</t>
+          <t>R69X-Unknown and unspecified causes of morbidity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>10753 (21.16%)</t>
+          <t>164190 (96.4%)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Diagnosis</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>X621-Assessment by uniprofessional team NEC</t>
+          <t>Other Main Diagnosis</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5850 (11.51%)</t>
+          <t>3716 (1.6%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Diagnosis</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>X483-Removal of plaster cast</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2851 (5.61%)</t>
+          <t>2415 (1.42%)</t>
         </is>
       </c>
     </row>
@@ -668,12 +668,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U134-Plain x-ray of joint</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2368 (4.66%)</t>
+          <t>119512 (70.17%)</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C873-Tomography evaluation of retina</t>
+          <t>Other Main Procedure</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1835 (3.61%)</t>
+          <t>25327 (14.53%)</t>
         </is>
       </c>
     </row>
@@ -702,12 +702,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U217-Plain x-ray NEC</t>
+          <t>X997-NA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1825 (3.59%)</t>
+          <t>10753 (6.31%)</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>X482-Change of plaster cast</t>
+          <t>X621-Assessment by uniprofessional team NEC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1439 (2.83%)</t>
+          <t>5850 (3.43%)</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U131-Bone densitometry</t>
+          <t>X483-Removal of plaster cast</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1372 (2.7%)</t>
+          <t>2851 (1.67%)</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>X622-Assessment by multiprofessional team NEC</t>
+          <t>U134-Plain x-ray of joint</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1291 (2.54%)</t>
+          <t>2368 (1.39%)</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>X481-Application of plaster cast</t>
+          <t>C873-Tomography evaluation of retina</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1241 (2.44%)</t>
+          <t>1835 (1.08%)</t>
         </is>
       </c>
     </row>
@@ -787,80 +787,80 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>X491-Application of splint NEC</t>
+          <t>U217-Plain x-ray NEC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>910 (1.79%)</t>
+          <t>1825 (1.07%)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>U135-Plain x-ray of bone</t>
+          <t>Trauma and Orthopaedics</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>693 (1.36%)</t>
+          <t>52766 (30.98%)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>U201-Transthoracic echocardiography</t>
+          <t>Allied Health Professional</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>622 (1.22%)</t>
+          <t>36128 (21.21%)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C794-Injection into vitreous body NEC</t>
+          <t>Other Main Specialty</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>550 (1.08%)</t>
+          <t>19557 (11.46%)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Main Procedure</t>
+          <t>Main Specialty</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>W925-Examination of joint NEC</t>
+          <t xml:space="preserve">Nursing </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>538 (1.06%)</t>
+          <t>11354 (6.67%)</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Trauma and Orthopaedics</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>52766 (31.57%)</t>
+          <t>10873 (6.38%)</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Allied Health Professional</t>
+          <t>Radiology</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>36128 (21.62%)</t>
+          <t>5310 (3.12%)</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Other Main Specialty</t>
+          <t>General Surgery</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19557 (11.69%)</t>
+          <t>4821 (2.83%)</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nursing </t>
+          <t>General Internal Medicine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>11354 (6.79%)</t>
+          <t>4544 (2.67%)</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Rheumatology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>10873 (6.51%)</t>
+          <t>4008 (2.35%)</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Radiology</t>
+          <t>Clinical Haematology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>5310 (3.18%)</t>
+          <t>3490 (2.05%)</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Surgery</t>
+          <t>Cardiology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4821 (2.88%)</t>
+          <t>3323 (1.95%)</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Internal Medicine</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>4544 (2.72%)</t>
+          <t>3179 (1.87%)</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Rheumatology</t>
+          <t>Dermatology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4008 (2.4%)</t>
+          <t>2540 (1.49%)</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Clinical Haematology</t>
+          <t>Geriatric Medicine</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3490 (2.09%)</t>
+          <t>2435 (1.43%)</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cardiology</t>
+          <t>Ear Nose and Throat</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3323 (1.99%)</t>
+          <t>2362 (1.39%)</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Gynaecology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2540 (1.52%)</t>
+          <t>1890 (1.11%)</t>
         </is>
       </c>
     </row>
@@ -1076,97 +1076,97 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Geriatric Medicine</t>
+          <t>Respiratory Medicine</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2435 (1.46%)</t>
+          <t>1741 (1.02%)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Main Specialty</t>
+          <t>OP Health Care Service Status</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Ear Nose and Throat</t>
+          <t>User</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2362 (1.41%)</t>
+          <t>20691 (89.55%)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Main Specialty</t>
+          <t>OP Health Care Service Status</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gynaecology</t>
+          <t>Non-User</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1890 (1.13%)</t>
+          <t>2415 (10.45%)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Main Specialty</t>
+          <t>Treatment Specialty</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Respiratory Medicine</t>
+          <t>Trauma and Orthopaedic Service</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1741 (1.04%)</t>
+          <t>54893 (32.23%)</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OP Health Care Service Status</t>
+          <t>Treatment Specialty</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>User</t>
+          <t>Physiotherapy Service</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>20691 (89.55%)</t>
+          <t>26819 (15.75%)</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OP Health Care Service Status</t>
+          <t>Treatment Specialty</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Non-User</t>
+          <t>Other Treatment Specialty</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2415 (10.45%)</t>
+          <t>24030 (14.11%)</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Trauma and Orthopaedic Service</t>
+          <t>Ophthalmology Service</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>54893 (33.05%)</t>
+          <t>11738 (6.89%)</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Physiotherapy Service</t>
+          <t>Diagnostic Imaging Service</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>26819 (16.15%)</t>
+          <t>5771 (3.39%)</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other Treatment Specialty</t>
+          <t>Rheumatology Service</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>24030 (14.46%)</t>
+          <t>5218 (3.06%)</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ophthalmology Service</t>
+          <t>Cardiology Service</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>11738 (7.07%)</t>
+          <t>4300 (2.52%)</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Diagnostic Imaging Service</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>5771 (3.47%)</t>
+          <t>4218 (2.48%)</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Rheumatology Service</t>
+          <t>Elderly Medicine Service</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>5218 (3.14%)</t>
+          <t>3317 (1.95%)</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cardiology Service</t>
+          <t>General Internal Medicine Service</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>4300 (2.59%)</t>
+          <t>3137 (1.84%)</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Elderly Medicine Service</t>
+          <t>Anticoagulant Service</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3317 (2%)</t>
+          <t>2957 (1.74%)</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Internal Medicine Service</t>
+          <t>Dermatology Service</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3137 (1.89%)</t>
+          <t>2845 (1.67%)</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Anticoagulant Service</t>
+          <t>Occupational Therapy Service</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2957 (1.78%)</t>
+          <t>2770 (1.63%)</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dermatology Service</t>
+          <t>Respiratory Medicine Service</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2845 (1.71%)</t>
+          <t>2529 (1.48%)</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Occupational Therapy Service</t>
+          <t>Ear Nose and Throat Service</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2770 (1.67%)</t>
+          <t>2505 (1.47%)</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Respiratory Medicine Service</t>
+          <t>Urology Service</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2529 (1.52%)</t>
+          <t>2112 (1.24%)</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ear Nose and Throat Service</t>
+          <t>Gynaecology Service</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2505 (1.51%)</t>
+          <t>2008 (1.18%)</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Urology Service</t>
+          <t>General Surgery Service</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2112 (1.27%)</t>
+          <t>1920 (1.13%)</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Gynaecology Service</t>
+          <t>Audiology Service</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2008 (1.21%)</t>
+          <t>1885 (1.11%)</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>General Surgery Service</t>
+          <t>Gastroenterology Service</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1920 (1.16%)</t>
+          <t>1840 (1.08%)</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Audiology Service</t>
+          <t>Intermediate Care Service</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1885 (1.13%)</t>
+          <t>1791 (1.05%)</t>
         </is>
       </c>
     </row>
@@ -1484,46 +1484,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gastroenterology Service</t>
+          <t>Neurology Service</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1840 (1.11%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Treatment Specialty</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Intermediate Care Service</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>1791 (1.08%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Treatment Specialty</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Neurology Service</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>1718 (1.03%)</t>
+          <t>1718 (1.01%)</t>
         </is>
       </c>
     </row>
